--- a/prompt/files/relatorios/Planilha_Status_Tarefas_MVP.xlsx
+++ b/prompt/files/relatorios/Planilha_Status_Tarefas_MVP.xlsx
@@ -52,13 +52,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
+      <color rgb="00991B1B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -101,14 +101,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-        <bgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -743,9 +743,9 @@
           <t>6h</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>A Fazer</t>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Alternância lógica da rota selecionada via botões da HUD já funcional no código.</t>
+          <t>WaypointPath.HighlightTemporarily(2.5s) + LineRenderer pulso via GameMatchManager.RequestPlayerSpawn.</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Shader leve ou decal/linha de textura projetada no chão indicando o caminho da rota escolhida.</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -893,9 +893,9 @@
           <t>6h</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>A Fazer</t>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Prefab TextMeshPro flutuante com animação de subida e fade out ao sofrer golpe.</t>
+          <t>Concluído: FloatingCombatTextManager pool zero-GC com subida e fade.</t>
         </is>
       </c>
     </row>
@@ -1043,9 +1043,9 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>A Fazer</t>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>MobaCameraController.cs configurado e ativo na Arena.</t>
+          <t>MobaCameraController.Instance.Shake() acionado em impactos críticos, explosões e Ultimate R.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Adicionar componente CinemachineImpulseSource disparado no dano crítico ou queda do Galinheiro.</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -1093,9 +1093,9 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>A Fazer</t>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>A partida inicia imediatamente ao carregar a cena Arena.</t>
+          <t>MatchCountdownIntro.cs overlay 3, 2, 1, LUTA! com som UI e cocoricó.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Overlay de contagem regressiva (3, 2, 1... LUTA!) travando joystick e spawns até zerar.</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
           <t>8h</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Em Andamento</t>
         </is>
@@ -1343,9 +1343,9 @@
           <t>6h</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>A Fazer</t>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>HUD de gameplay ativa com botões de rota e joystick.</t>
+          <t>MatchPauseMenuController Time.timeScale 0/1 + painel Reiniciar/Sair e sliders volume.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Botão de engrenagem na HUD para pausar Time.timeScale = 0 e modal com 'Reiniciar' e 'Sair'.</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -1393,9 +1393,9 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>A Fazer</t>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Tratamento de exceções locais em chamadas RPC com fallbacks offline.</t>
+          <t>NetworkStatusMonitor poll internetReachability + banner vermelho/verde topo.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Listener de conectividade exibindo toast/popup de alerta se a conexão for perdida durante a transação.</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -1593,9 +1593,9 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>A Fazer</t>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Transações construídas no TransactionManager.cs.</t>
+          <t>TransactionManager ComputeBudgetProgram.SetComputeUnitLimit(200_000) no builder.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Adicionar ComputeBudgetProgram.SetComputeUnitLimit(50_000) no builder para garantir transação ultra rápida e econômica.</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -1893,9 +1893,9 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Desabilitação de cliques e mensagem textual 'Processando registro on-chain...' exibida no Presenter.</t>
+          <t>Vitoria/DerrotaPresenter SetStatus processando + bloqueio botão durante sendTransaction.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Modal pop-up dedicado com spinner gráfico bloqueando a tela inteira durante confirmação de bloco.</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -2043,9 +2043,9 @@
           <t>6h</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>A Fazer</t>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2060,12 +2060,12 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Lista e biblioteca de efeitos sonoros catalogadas na documentação do projeto.</t>
+          <t>AudioManager.cs pool 12 SFX + BGM/UI + procedural fallback conectado a Milo/Axel/Minions/Galinheiro.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Criar script AudioManager.cs com pool de AudioSource disparados nos eventos de spawn, ataque e vitória/derrota.</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -2093,9 +2093,9 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>A Fazer</t>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Estrutura de salvamento base pronta.</t>
+          <t>AudioManager PlayerPrefs Master/Bgm/Sfx + sliders em MatchPauseMenuController.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Sliders de volume Master, BGM e SFX na UI salvando configurações no PlayerPrefs.</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -2243,9 +2243,9 @@
           <t>8h</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>PlayerSettings preparado para Android ARM64, Target SDK 34 e orientação Landscape.</t>
+          <t>AndroidReleaseBuildPipeline: PlayerSettings ARM64/Landscape + BuildPipeline menu Build APK.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Criar script de automação de build headless em lote (BuildScript.cs).</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -2293,9 +2293,9 @@
           <t>6h</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>A Fazer</t>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Configurações base de build do Unity.</t>
+          <t>AndroidReleaseBuildPipeline: IL2CPP + ARM64 + ASTC + stripEngineCode.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Habilitar Scripting Backend como IL2CPP no Build Settings e definir compressão padrão de textura para ASTC.</t>
+          <t>Concluído e operando; sem pendências.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
           <t>8h</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>A Fazer</t>
         </is>
@@ -2393,7 +2393,7 @@
           <t>6h</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>A Fazer</t>
         </is>
@@ -2443,7 +2443,7 @@
           <t>6h</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>A Fazer</t>
         </is>
@@ -2493,7 +2493,7 @@
           <t>2h</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>A Fazer</t>
         </is>
